--- a/tests/vlaanderen/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaalproduct_Auto.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaalproduct_Auto.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>108584</v>
+        <v>126654</v>
       </c>
       <c r="C2">
-        <v>205067</v>
+        <v>224089</v>
       </c>
       <c r="D2">
-        <v>277911</v>
+        <v>290574</v>
       </c>
       <c r="E2">
-        <v>308393</v>
+        <v>320441</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>132876</v>
+        <v>157653</v>
       </c>
       <c r="C3">
-        <v>246370</v>
+        <v>269843</v>
       </c>
       <c r="D3">
-        <v>328452</v>
+        <v>344370</v>
       </c>
       <c r="E3">
-        <v>366456</v>
+        <v>381704</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>133635</v>
+        <v>138250</v>
       </c>
       <c r="C4">
-        <v>247400</v>
+        <v>251361</v>
       </c>
       <c r="D4">
-        <v>328279</v>
+        <v>329953</v>
       </c>
       <c r="E4">
-        <v>365745</v>
+        <v>366928</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>106740</v>
+        <v>117047</v>
       </c>
       <c r="C5">
-        <v>183311</v>
+        <v>194740</v>
       </c>
       <c r="D5">
-        <v>231308</v>
+        <v>236484</v>
       </c>
       <c r="E5">
-        <v>257446</v>
+        <v>260719</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>92647</v>
+        <v>101538</v>
       </c>
       <c r="C6">
-        <v>160532</v>
+        <v>168068</v>
       </c>
       <c r="D6">
-        <v>204809</v>
+        <v>208519</v>
       </c>
       <c r="E6">
-        <v>225230</v>
+        <v>227694</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>10709</v>
+        <v>11260</v>
       </c>
       <c r="C7">
-        <v>17652</v>
+        <v>18179</v>
       </c>
       <c r="D7">
-        <v>22080</v>
+        <v>22433</v>
       </c>
       <c r="E7">
-        <v>23932</v>
+        <v>24297</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>235113</v>
+        <v>382585</v>
       </c>
       <c r="C8">
-        <v>595186</v>
+        <v>752912</v>
       </c>
       <c r="D8">
-        <v>917489</v>
+        <v>1053642</v>
       </c>
       <c r="E8">
-        <v>1179527</v>
+        <v>1229917</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>124963</v>
+        <v>154207</v>
       </c>
       <c r="C9">
-        <v>220551</v>
+        <v>243710</v>
       </c>
       <c r="D9">
-        <v>287667</v>
+        <v>297055</v>
       </c>
       <c r="E9">
-        <v>320144</v>
+        <v>325955</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>59458</v>
+        <v>65592</v>
       </c>
       <c r="C10">
-        <v>99558</v>
+        <v>104154</v>
       </c>
       <c r="D10">
-        <v>127373</v>
+        <v>129658</v>
       </c>
       <c r="E10">
-        <v>136703</v>
+        <v>138610</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>10987</v>
+        <v>12100</v>
       </c>
       <c r="C11">
-        <v>17411</v>
+        <v>18140</v>
       </c>
       <c r="D11">
-        <v>21997</v>
+        <v>22410</v>
       </c>
       <c r="E11">
-        <v>25472</v>
+        <v>25927</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>27332</v>
+        <v>32034</v>
       </c>
       <c r="C12">
-        <v>46896</v>
+        <v>49408</v>
       </c>
       <c r="D12">
-        <v>58869</v>
+        <v>59477</v>
       </c>
       <c r="E12">
-        <v>62168</v>
+        <v>62504</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>33402</v>
+        <v>36745</v>
       </c>
       <c r="C13">
-        <v>55469</v>
+        <v>57771</v>
       </c>
       <c r="D13">
-        <v>71653</v>
+        <v>72841</v>
       </c>
       <c r="E13">
-        <v>77810</v>
+        <v>78796</v>
       </c>
     </row>
   </sheetData>
